--- a/samples/edge-cases/edge-order-form/template.xlsx
+++ b/samples/edge-cases/edge-order-form/template.xlsx
@@ -1077,7 +1077,7 @@
       </c>
       <c r="G10" s="14">
         <f>IF(D10="","",D10*F10)</f>
-        <v>48000.0</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="11">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G11" s="14">
         <f>IF(D11="","",D11*F11)</f>
-        <v>25600.0</v>
+        <v>25600</v>
       </c>
     </row>
     <row r="12">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="G12" s="14">
         <f>IF(D12="","",D12*F12)</f>
-        <v>-3000.0</v>
+        <v>-3000</v>
       </c>
     </row>
     <row r="13">
@@ -1209,7 +1209,7 @@
       <c r="F18" s="20" t="n"/>
       <c r="G18" s="21">
         <f>SUM(G10:G17)</f>
-        <v>70600.0</v>
+        <v>70600</v>
       </c>
     </row>
     <row r="19">
@@ -1221,7 +1221,7 @@
       <c r="F19" s="20" t="n"/>
       <c r="G19" s="21">
         <f>ROUNDDOWN(G18*0.1,0)</f>
-        <v>7060.0</v>
+        <v>7060</v>
       </c>
     </row>
     <row r="20">
@@ -1233,7 +1233,7 @@
       <c r="F20" s="23" t="n"/>
       <c r="G20" s="24">
         <f>G18+G19</f>
-        <v>77660.0</v>
+        <v>77660</v>
       </c>
     </row>
     <row r="22">
